--- a/data/trans_dic/P71_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 16,75</t>
+          <t>10,65; 16,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 33,79</t>
+          <t>24,26; 33,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,01; 33,8</t>
+          <t>24,88; 33,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 19,78</t>
+          <t>8,36; 19,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 25,0</t>
+          <t>17,89; 25,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 30,42</t>
+          <t>21,8; 30,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,54; 32,11</t>
+          <t>23,71; 32,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 25,49</t>
+          <t>12,99; 25,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,96; 19,92</t>
+          <t>14,97; 19,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,31; 30,33</t>
+          <t>24,44; 30,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,83; 32,01</t>
+          <t>25,81; 32,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,05</t>
+          <t>11,79; 19,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,3</t>
+          <t>14,39; 19,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 33,32</t>
+          <t>26,53; 33,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 38,96</t>
+          <t>30,63; 38,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 17,66</t>
+          <t>9,52; 17,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,68; 24,52</t>
+          <t>18,04; 24,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 37,64</t>
+          <t>30,01; 38,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,18; 35,91</t>
+          <t>28,48; 35,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 52,24</t>
+          <t>14,28; 55,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 21,43</t>
+          <t>16,81; 21,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,45; 34,43</t>
+          <t>28,92; 34,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,88; 36,1</t>
+          <t>30,86; 36,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,52; 38,45</t>
+          <t>13,5; 39,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,0</t>
+          <t>12,18; 17,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,09; 38,9</t>
+          <t>31,64; 38,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,73; 36,37</t>
+          <t>29,24; 36,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 16,37</t>
+          <t>11,0; 16,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,52; 29,46</t>
+          <t>22,23; 28,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,93; 39,22</t>
+          <t>31,78; 39,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,35; 40,51</t>
+          <t>33,61; 41,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 16,03</t>
+          <t>9,91; 16,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 22,65</t>
+          <t>18,14; 22,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,75; 38,06</t>
+          <t>32,63; 37,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,15; 37,38</t>
+          <t>32,04; 37,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,53</t>
+          <t>11,1; 15,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 19,64</t>
+          <t>12,69; 19,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,75; 37,78</t>
+          <t>29,68; 38,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,99; 42,9</t>
+          <t>34,86; 42,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 13,62</t>
+          <t>4,11; 13,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,23; 30,33</t>
+          <t>22,58; 30,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 38,49</t>
+          <t>29,58; 38,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,2; 46,54</t>
+          <t>38,66; 46,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 17,04</t>
+          <t>12,23; 17,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,8</t>
+          <t>18,82; 23,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 36,43</t>
+          <t>30,87; 36,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,09; 43,77</t>
+          <t>37,62; 43,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 14,32</t>
+          <t>6,99; 14,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 27,94</t>
+          <t>19,37; 27,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,87; 35,42</t>
+          <t>25,68; 35,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,84; 39,74</t>
+          <t>30,93; 39,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,45</t>
+          <t>14,17; 20,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,6; 33,42</t>
+          <t>24,29; 33,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 34,04</t>
+          <t>25,11; 33,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,61; 42,89</t>
+          <t>33,53; 43,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,44; 22,71</t>
+          <t>17,6; 22,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,32; 29,51</t>
+          <t>22,86; 29,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,83; 33,2</t>
+          <t>26,4; 32,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,5; 39,59</t>
+          <t>33,44; 39,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,7; 20,54</t>
+          <t>16,65; 20,74</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,91; 28,53</t>
+          <t>19,18; 29,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,24; 28,57</t>
+          <t>17,96; 28,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 34,07</t>
+          <t>24,34; 34,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,4; 12,63</t>
+          <t>7,57; 12,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,35; 45,72</t>
+          <t>35,85; 45,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,38; 31,77</t>
+          <t>22,38; 32,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,35; 36,69</t>
+          <t>27,17; 36,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 12,89</t>
+          <t>2,69; 12,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,27; 36,57</t>
+          <t>29,37; 36,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,4; 28,76</t>
+          <t>21,72; 28,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,99; 34,03</t>
+          <t>26,96; 34,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,51</t>
+          <t>4,61; 11,79</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,72; 37,46</t>
+          <t>24,85; 37,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,33; 33,75</t>
+          <t>21,02; 33,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,31; 33,71</t>
+          <t>23,05; 33,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,47</t>
+          <t>6,35; 12,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,38; 47,63</t>
+          <t>36,33; 47,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,63; 36,25</t>
+          <t>26,54; 35,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,93; 40,98</t>
+          <t>30,44; 40,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,46; 22,21</t>
+          <t>16,64; 22,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,34; 42,21</t>
+          <t>33,81; 42,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,96; 33,68</t>
+          <t>26,25; 34,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,93; 36,62</t>
+          <t>29,33; 36,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,15; 17,28</t>
+          <t>13,25; 17,19</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,6; 19,4</t>
+          <t>16,8; 19,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,1; 32,22</t>
+          <t>28,99; 32,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,14</t>
+          <t>31,77; 35,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,64</t>
+          <t>9,29; 13,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,34; 29,49</t>
+          <t>26,36; 29,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 33,27</t>
+          <t>29,9; 33,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,14; 37,32</t>
+          <t>33,97; 37,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,23</t>
+          <t>13,86; 21,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,85; 23,98</t>
+          <t>22,05; 24,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,95; 32,27</t>
+          <t>30,02; 32,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33,49; 35,86</t>
+          <t>33,58; 35,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,44</t>
+          <t>12,67; 17,28</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51969; 81355</t>
+          <t>51753; 80678</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112453; 152486</t>
+          <t>109456; 149136</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103511; 139879</t>
+          <t>102980; 140030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32094; 75599</t>
+          <t>31973; 73008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82022; 115010</t>
+          <t>82294; 115515</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91110; 130575</t>
+          <t>93575; 130031</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92506; 126189</t>
+          <t>93189; 129470</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40836; 79089</t>
+          <t>40309; 80264</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141487; 188411</t>
+          <t>141629; 187102</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>214053; 267108</t>
+          <t>215174; 267511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208424; 258279</t>
+          <t>208289; 260011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80367; 138891</t>
+          <t>81650; 137298</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>106468; 148556</t>
+          <t>105270; 144884</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>182135; 228299</t>
+          <t>181749; 229818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>182544; 230064</t>
+          <t>180868; 229627</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40006; 74364</t>
+          <t>40101; 74053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>108524; 150490</t>
+          <t>110700; 152209</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>182004; 229708</t>
+          <t>183140; 232414</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>158257; 201661</t>
+          <t>159956; 201820</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71515; 263386</t>
+          <t>72023; 280836</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>228401; 288364</t>
+          <t>226153; 287009</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381513; 446087</t>
+          <t>374685; 442962</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>355811; 415841</t>
+          <t>355518; 417640</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>125065; 355742</t>
+          <t>124947; 362625</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77054; 114328</t>
+          <t>77336; 113328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211092; 264093</t>
+          <t>214822; 263263</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191374; 242285</t>
+          <t>194753; 243689</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57263; 87558</t>
+          <t>58818; 88512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>152600; 199654</t>
+          <t>150654; 195683</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>225749; 277289</t>
+          <t>224661; 278253</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>219400; 266516</t>
+          <t>221130; 270233</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57073; 94531</t>
+          <t>58428; 94550</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>238862; 297360</t>
+          <t>238207; 298620</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>453828; 527431</t>
+          <t>452291; 525942</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>425627; 494940</t>
+          <t>424189; 494505</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>124516; 174630</t>
+          <t>124853; 172607</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65562; 101396</t>
+          <t>65528; 100692</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>182843; 232201</t>
+          <t>182432; 234066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>224676; 275473</t>
+          <t>223856; 274898</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38040; 119837</t>
+          <t>36184; 122315</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>112367; 153317</t>
+          <t>114140; 154020</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>182122; 236259</t>
+          <t>181576; 233782</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>247531; 301587</t>
+          <t>250528; 303759</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83322; 115306</t>
+          <t>82802; 116712</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191114; 243205</t>
+          <t>192279; 242044</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>377123; 447554</t>
+          <t>379254; 452198</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>491410; 564664</t>
+          <t>485263; 564875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>110736; 222934</t>
+          <t>108842; 221488</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73162; 105100</t>
+          <t>72847; 104329</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>109915; 150474</t>
+          <t>109091; 149672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146423; 188684</t>
+          <t>146847; 189536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79339; 112902</t>
+          <t>78224; 112148</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97657; 132633</t>
+          <t>96410; 132277</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>111104; 150595</t>
+          <t>111112; 150369</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>166236; 212130</t>
+          <t>165838; 214366</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94216; 122668</t>
+          <t>95078; 122693</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180275; 228099</t>
+          <t>176744; 225179</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>232714; 287951</t>
+          <t>228953; 282860</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>324719; 383727</t>
+          <t>324162; 387609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>182425; 224352</t>
+          <t>181838; 226574</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53482; 80661</t>
+          <t>54239; 82633</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55722; 87283</t>
+          <t>54884; 85955</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78171; 110903</t>
+          <t>79227; 111617</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27023; 46125</t>
+          <t>27651; 45779</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>117393; 151843</t>
+          <t>119062; 151768</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79021; 112143</t>
+          <t>78995; 113544</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>102331; 137273</t>
+          <t>101660; 137635</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16402; 77941</t>
+          <t>16290; 77275</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>179989; 224863</t>
+          <t>180606; 224003</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>140950; 189370</t>
+          <t>143017; 189821</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188807; 238062</t>
+          <t>188607; 239068</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40767; 111646</t>
+          <t>44686; 114330</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50186; 76067</t>
+          <t>50446; 76793</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53065; 83960</t>
+          <t>52305; 82274</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59310; 85775</t>
+          <t>58657; 85340</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17561; 32207</t>
+          <t>17818; 34580</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>116413; 156711</t>
+          <t>119527; 155729</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>102997; 140227</t>
+          <t>102679; 139133</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>119037; 162994</t>
+          <t>121043; 162129</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>68754; 92796</t>
+          <t>69526; 92184</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>177407; 224584</t>
+          <t>179893; 223629</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>165019; 214047</t>
+          <t>166837; 216567</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>188644; 238829</t>
+          <t>191255; 240465</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>91854; 120677</t>
+          <t>92553; 120037</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>536405; 626782</t>
+          <t>542936; 627470</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>992066; 1098336</t>
+          <t>988394; 1099963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1075363; 1183427</t>
+          <t>1069847; 1184093</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>329674; 465813</t>
+          <t>317457; 466090</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>873035; 977713</t>
+          <t>873730; 977973</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1061306; 1178750</t>
+          <t>1059267; 1179250</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1203999; 1316227</t>
+          <t>1198004; 1315886</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>518264; 809900</t>
+          <t>504971; 788405</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1429935; 1569869</t>
+          <t>1443179; 1577379</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2081858; 2243353</t>
+          <t>2087027; 2239782</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2308918; 2472259</t>
+          <t>2314822; 2470344</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>904865; 1231268</t>
+          <t>894116; 1219741</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P71_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 16,61</t>
+          <t>10,09; 16,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,26; 33,05</t>
+          <t>24,57; 32,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,88; 33,83</t>
+          <t>24,7; 34,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 19,1</t>
+          <t>10,58; 22,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 25,11</t>
+          <t>17,49; 24,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 30,29</t>
+          <t>21,49; 29,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,95</t>
+          <t>23,66; 32,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 25,87</t>
+          <t>13,33; 25,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,97; 19,78</t>
+          <t>14,88; 19,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 30,38</t>
+          <t>24,03; 30,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,81; 32,23</t>
+          <t>25,61; 31,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,79; 19,82</t>
+          <t>13,43; 21,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,39; 19,8</t>
+          <t>14,46; 20,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,53; 33,54</t>
+          <t>26,38; 33,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,63; 38,89</t>
+          <t>31,1; 38,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,59</t>
+          <t>10,37; 18,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,04; 24,8</t>
+          <t>17,99; 24,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 38,08</t>
+          <t>29,9; 37,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,48; 35,94</t>
+          <t>28,43; 36,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 55,7</t>
+          <t>13,74; 21,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 21,33</t>
+          <t>16,8; 21,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,92; 34,19</t>
+          <t>29,06; 34,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,86; 36,25</t>
+          <t>30,96; 36,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 39,19</t>
+          <t>13,03; 18,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,84</t>
+          <t>12,05; 18,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,64; 38,78</t>
+          <t>31,19; 38,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,24; 36,58</t>
+          <t>29,05; 36,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 16,55</t>
+          <t>12,89; 19,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,23; 28,87</t>
+          <t>22,35; 29,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,36</t>
+          <t>32,32; 39,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,61; 41,08</t>
+          <t>33,45; 41,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 16,03</t>
+          <t>13,1; 17,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,14; 22,75</t>
+          <t>18,29; 23,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,63; 37,95</t>
+          <t>32,51; 38,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,04; 37,35</t>
+          <t>32,29; 37,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,35</t>
+          <t>13,76; 17,65</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 19,5</t>
+          <t>13,03; 19,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 38,08</t>
+          <t>29,81; 37,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,86; 42,81</t>
+          <t>34,92; 42,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,91</t>
+          <t>11,47; 17,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,58; 30,47</t>
+          <t>22,65; 30,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,58; 38,08</t>
+          <t>30,11; 37,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,66; 46,88</t>
+          <t>38,62; 46,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,24</t>
+          <t>13,01; 17,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,82; 23,69</t>
+          <t>18,46; 23,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,87; 36,81</t>
+          <t>30,93; 36,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,62; 43,79</t>
+          <t>37,79; 43,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 14,23</t>
+          <t>13,03; 16,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 27,74</t>
+          <t>19,46; 27,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,68; 35,23</t>
+          <t>25,39; 34,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,93; 39,92</t>
+          <t>30,6; 39,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 20,31</t>
+          <t>15,01; 21,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 33,33</t>
+          <t>24,8; 34,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 33,99</t>
+          <t>25,04; 34,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 43,35</t>
+          <t>32,87; 42,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 22,72</t>
+          <t>17,82; 22,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,86; 29,13</t>
+          <t>23,03; 29,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,4; 32,61</t>
+          <t>26,55; 33,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,44; 39,99</t>
+          <t>33,33; 40,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 20,74</t>
+          <t>17,13; 21,04</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,22</t>
+          <t>18,62; 28,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,96; 28,13</t>
+          <t>17,88; 27,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,34; 34,29</t>
+          <t>24,35; 35,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,57; 12,54</t>
+          <t>7,85; 12,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,85; 45,7</t>
+          <t>35,75; 45,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,38; 32,16</t>
+          <t>22,56; 32,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,17; 36,79</t>
+          <t>27,2; 36,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,78</t>
+          <t>10,06; 14,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,37; 36,43</t>
+          <t>29,27; 36,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,72; 28,82</t>
+          <t>21,63; 28,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,96; 34,17</t>
+          <t>27,46; 34,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,79</t>
+          <t>9,54; 12,84</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,85; 37,82</t>
+          <t>24,86; 37,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,02; 33,07</t>
+          <t>21,24; 33,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,05; 33,54</t>
+          <t>23,37; 33,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,32</t>
+          <t>6,16; 11,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,33; 47,33</t>
+          <t>35,61; 47,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,54; 35,97</t>
+          <t>26,46; 36,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,44; 40,77</t>
+          <t>30,25; 40,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,07</t>
+          <t>16,98; 22,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,81; 42,03</t>
+          <t>33,59; 42,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,25; 34,07</t>
+          <t>25,83; 33,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,33; 36,87</t>
+          <t>29,17; 36,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 17,19</t>
+          <t>13,31; 17,06</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,8; 19,42</t>
+          <t>16,71; 19,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,99; 32,27</t>
+          <t>29,01; 32,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,77; 35,16</t>
+          <t>31,84; 35,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,64</t>
+          <t>13,0; 15,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,36; 29,5</t>
+          <t>26,32; 29,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,9; 33,29</t>
+          <t>29,96; 33,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,97; 37,31</t>
+          <t>34,08; 37,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,86; 21,64</t>
+          <t>15,73; 18,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,05; 24,1</t>
+          <t>22,0; 24,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,02; 32,22</t>
+          <t>29,98; 32,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33,58; 35,83</t>
+          <t>33,44; 35,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,28</t>
+          <t>14,73; 16,53</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>63250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>107788</t>
+          <t>129564</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51753; 80678</t>
+          <t>49020; 80823</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109456; 149136</t>
+          <t>110862; 148251</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102980; 140030</t>
+          <t>102222; 141171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31973; 73008</t>
+          <t>41305; 89498</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82294; 115515</t>
+          <t>80448; 114091</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93575; 130031</t>
+          <t>92263; 128761</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93189; 129470</t>
+          <t>92977; 126528</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40309; 80264</t>
+          <t>47940; 90510</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141629; 187102</t>
+          <t>140761; 186681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>215174; 267511</t>
+          <t>211590; 268989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208289; 260011</t>
+          <t>206668; 257141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81650; 137298</t>
+          <t>100707; 162261</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>136342</t>
+          <t>85349</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>191783</t>
+          <t>150684</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>105270; 144884</t>
+          <t>105769; 148325</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181749; 229818</t>
+          <t>180740; 229786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>180868; 229627</t>
+          <t>183648; 229934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40101; 74053</t>
+          <t>49193; 86869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>110700; 152209</t>
+          <t>110429; 152921</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>183140; 232414</t>
+          <t>182491; 229657</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>159956; 201820</t>
+          <t>159666; 204006</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72023; 280836</t>
+          <t>67499; 105621</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>226153; 287009</t>
+          <t>226056; 285458</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>374685; 442962</t>
+          <t>376495; 446427</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>355518; 417640</t>
+          <t>356656; 421015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>124947; 362625</t>
+          <t>125814; 177383</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72824</t>
+          <t>98651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>95290</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>151490</t>
+          <t>193941</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77336; 113328</t>
+          <t>76529; 114584</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>214822; 263263</t>
+          <t>211738; 263902</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194753; 243689</t>
+          <t>193540; 241423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58818; 88512</t>
+          <t>79320; 117762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>150654; 195683</t>
+          <t>151460; 197141</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>224661; 278253</t>
+          <t>228546; 277990</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>221130; 270233</t>
+          <t>220037; 269976</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58428; 94550</t>
+          <t>81281; 111095</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>238207; 298620</t>
+          <t>240163; 302563</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>452291; 525942</t>
+          <t>450610; 526794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>424189; 494505</t>
+          <t>427485; 495975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>124853; 172607</t>
+          <t>170034; 218094</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>97097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97776</t>
+          <t>111691</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>178369</t>
+          <t>208788</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65528; 100692</t>
+          <t>67293; 100916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>182432; 234066</t>
+          <t>183195; 231064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>223856; 274898</t>
+          <t>224236; 273841</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36184; 122315</t>
+          <t>79290; 118053</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>114140; 154020</t>
+          <t>114454; 153239</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>181576; 233782</t>
+          <t>184830; 232764</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>250528; 303759</t>
+          <t>250260; 302044</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82802; 116712</t>
+          <t>95361; 127182</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192279; 242044</t>
+          <t>188595; 242492</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>379254; 452198</t>
+          <t>379973; 453062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>485263; 564875</t>
+          <t>487572; 559172</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108842; 221488</t>
+          <t>185619; 234449</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95138</t>
+          <t>107129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>121923</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>202910</t>
+          <t>229052</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72847; 104329</t>
+          <t>73184; 105125</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>109091; 149672</t>
+          <t>107891; 146184</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146847; 189536</t>
+          <t>145277; 189273</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78224; 112148</t>
+          <t>89814; 129128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96410; 132277</t>
+          <t>98437; 135130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>111112; 150369</t>
+          <t>110760; 151967</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>165838; 214366</t>
+          <t>162572; 211157</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95078; 122693</t>
+          <t>107324; 138348</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>176744; 225179</t>
+          <t>178006; 228609</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228953; 282860</t>
+          <t>230256; 286868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>324162; 387609</t>
+          <t>323082; 390169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>181838; 226574</t>
+          <t>205679; 252637</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>40673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>93904</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54239; 82633</t>
+          <t>52653; 80354</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54884; 85955</t>
+          <t>54623; 85381</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79227; 111617</t>
+          <t>79239; 114054</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27651; 45779</t>
+          <t>31687; 50581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>119062; 151768</t>
+          <t>118718; 150124</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78995; 113544</t>
+          <t>79631; 114089</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>101660; 137635</t>
+          <t>101761; 136497</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16290; 77275</t>
+          <t>43739; 63431</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>180606; 224003</t>
+          <t>179942; 224216</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>143017; 189821</t>
+          <t>142476; 188829</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188607; 239068</t>
+          <t>192118; 238424</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44686; 114330</t>
+          <t>79986; 107631</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>80804</t>
+          <t>89782</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>105439</t>
+          <t>116386</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50446; 76793</t>
+          <t>50484; 76831</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52305; 82274</t>
+          <t>52842; 83611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58657; 85340</t>
+          <t>59467; 84305</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17818; 34580</t>
+          <t>18979; 35972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119527; 155729</t>
+          <t>117174; 156022</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>102679; 139133</t>
+          <t>102343; 139332</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>121043; 162129</t>
+          <t>120302; 162683</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>69526; 92184</t>
+          <t>77434; 102526</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179893; 223629</t>
+          <t>178735; 224609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166837; 216567</t>
+          <t>164165; 212607</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>191255; 240465</t>
+          <t>190253; 240198</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92553; 120037</t>
+          <t>101653; 130305</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>542936; 627470</t>
+          <t>539752; 628141</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>988394; 1099963</t>
+          <t>989070; 1096750</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1069847; 1184093</t>
+          <t>1072306; 1181665</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>317457; 466090</t>
+          <t>452722; 545741</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>873730; 977973</t>
+          <t>872523; 974556</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1059267; 1179250</t>
+          <t>1061488; 1178397</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1198004; 1315886</t>
+          <t>1201964; 1319856</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>504971; 788405</t>
+          <t>581647; 665420</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1443179; 1577379</t>
+          <t>1440326; 1578494</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2087027; 2239782</t>
+          <t>2084308; 2246181</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2314822; 2470344</t>
+          <t>2305668; 2468465</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>894116; 1219741</t>
+          <t>1057634; 1186356</t>
         </is>
       </c>
     </row>
